--- a/data/employees/EMP070/AST-EMP070-06.xlsx
+++ b/data/employees/EMP070/AST-EMP070-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Skyler Chen (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Skyler Chen | Role: Specialist | Location: Fremont | Date: 2025-03-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP070</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp070 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>79</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP070</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp070 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Mentoring</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>73</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP070</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp070 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>92</v>
+        <v>75</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP070</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp070 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>66</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>68</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>65</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>89</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>88</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>89</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>94</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>63</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>81</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>61</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>70</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>94</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>68</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp070 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>68</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP070</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP070 contributes to ast emp070 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>